--- a/artfynd/A 32207-2022 artfynd.xlsx
+++ b/artfynd/A 32207-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32207-2022 artfynd.xlsx
+++ b/artfynd/A 32207-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>95125474</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408746.1848883344</v>
+        <v>408746</v>
       </c>
       <c r="R2" t="n">
-        <v>7018510.663897458</v>
+        <v>7018511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>95125545</v>
       </c>
       <c r="B3" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408721.7507002327</v>
+        <v>408722</v>
       </c>
       <c r="R3" t="n">
-        <v>7018539.270206216</v>
+        <v>7018539</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +882,7 @@
         <v>95125579</v>
       </c>
       <c r="B4" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408735.0255017356</v>
+        <v>408735</v>
       </c>
       <c r="R4" t="n">
-        <v>7018514.582238382</v>
+        <v>7018515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,19 +951,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,12 +984,7 @@
         <v>95125629</v>
       </c>
       <c r="B5" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408730.2819745846</v>
+        <v>408730</v>
       </c>
       <c r="R5" t="n">
-        <v>7018490.405447366</v>
+        <v>7018490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,19 +1053,9 @@
           <t>2021-07-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 32207-2022 artfynd.xlsx
+++ b/artfynd/A 32207-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95125474</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95125545</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95125579</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95125629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>